--- a/data/trans_camb/IP07_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,91</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-5,62</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,98</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-6,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>-5,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 4,0</t>
+          <t>-8,19; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 11,23</t>
+          <t>-5,73; 11,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 4,03</t>
+          <t>-13,71; 5,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 10,08</t>
+          <t>-15,79; 3,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 11,2</t>
+          <t>-6,68; 10,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 4,44</t>
+          <t>-14,88; 3,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 3,94</t>
+          <t>-9,61; 3,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 8,79</t>
+          <t>-4,4; 8,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 2,7</t>
+          <t>-12,23; 1,19</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-5,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-6,86%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-6,11%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5,46%</t>
+          <t>-7,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-5,72%</t>
+          <t>-6,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 5,01</t>
+          <t>-9,38; 12,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 14,78</t>
+          <t>-6,7; 14,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 5,48</t>
+          <t>-16,04; 6,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 13,07</t>
+          <t>-18,3; 4,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 14,5</t>
+          <t>-7,96; 14,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 5,71</t>
+          <t>-17,63; 4,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 4,88</t>
+          <t>-11,27; 4,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 11,1</t>
+          <t>-5,16; 10,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 3,42</t>
+          <t>-14,42; 1,42</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>19,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,69</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 11,23</t>
+          <t>-10,34; 8,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 27,53</t>
+          <t>-4,13; 12,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 10,3</t>
+          <t>-10,89; 8,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 7,7</t>
+          <t>-9,08; 11,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 11,32</t>
+          <t>10,73; 27,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 8,35</t>
+          <t>-11,02; 9,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 6,8</t>
+          <t>-6,78; 7,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 16,95</t>
+          <t>5,39; 17,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 6,15</t>
+          <t>-7,63; 7,16</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-1,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-1,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>25,36%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,61%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,93%</t>
+          <t>-0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>-0,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 16,32</t>
+          <t>-11,83; 11,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 41,35</t>
+          <t>-4,75; 16,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 14,47</t>
+          <t>-12,57; 11,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 10,03</t>
+          <t>-11,4; 16,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 14,59</t>
+          <t>13,58; 39,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 10,83</t>
+          <t>-13,92; 14,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 9,01</t>
+          <t>-8,22; 9,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 22,78</t>
+          <t>6,5; 23,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 8,27</t>
+          <t>-9,29; 9,6</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,87</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>9,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>6,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 8,86</t>
+          <t>-9,12; 10,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 21,0</t>
+          <t>7,32; 25,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 16,6</t>
+          <t>-4,31; 17,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 11,79</t>
+          <t>-12,27; 8,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 24,75</t>
+          <t>-0,9; 19,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 17,77</t>
+          <t>-5,78; 17,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 7,55</t>
+          <t>-7,77; 7,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 20,05</t>
+          <t>7,23; 21,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,45</t>
+          <t>-1,96; 14,31</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-2,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>12,04%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,52%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 12,08</t>
+          <t>-11,33; 14,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 29,31</t>
+          <t>8,93; 36,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 23,05</t>
+          <t>-5,42; 24,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 17,25</t>
+          <t>-14,44; 12,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,09; 35,53</t>
+          <t>-0,99; 27,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 26,29</t>
+          <t>-7,06; 23,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 10,34</t>
+          <t>-9,76; 10,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,74; 27,56</t>
+          <t>8,71; 29,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 18,5</t>
+          <t>-2,32; 19,62</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-6,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,04</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,79</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-6,48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-6,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,04</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-1,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,66; -0,08</t>
+          <t>-13,34; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,27</t>
+          <t>2,71; 16,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 8,81</t>
+          <t>-8,16; 7,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 0,35</t>
+          <t>-13,17; 0,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 15,27</t>
+          <t>-0,7; 11,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 6,72</t>
+          <t>-9,44; 4,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -1,63</t>
+          <t>-11,33; -1,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,4</t>
+          <t>2,55; 11,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,5</t>
+          <t>-6,43; 3,08</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-8,28%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-1,02%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-8,26%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>6,57%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,06%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-8,28%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,09%</t>
+          <t>-2,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,57%</t>
+          <t>-1,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,62; -0,07</t>
+          <t>-16,33; 1,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 15,11</t>
+          <t>3,3; 21,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 11,71</t>
+          <t>-10,09; 9,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 0,66</t>
+          <t>-16,36; 0,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 20,67</t>
+          <t>-0,66; 15,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 9,15</t>
+          <t>-11,54; 6,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,57; -2,19</t>
+          <t>-14,29; -1,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 15,03</t>
+          <t>3,26; 15,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 7,33</t>
+          <t>-8,1; 4,11</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11,32</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,66</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>8,87</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11,32</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 12,12</t>
+          <t>-7,92; 9,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 17,53</t>
+          <t>2,97; 19,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 11,12</t>
+          <t>-18,08; 6,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 9,61</t>
+          <t>-4,91; 12,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 19,98</t>
+          <t>1,33; 17,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 8,43</t>
+          <t>-6,21; 11,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,06</t>
+          <t>-4,18; 8,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 15,4</t>
+          <t>3,67; 15,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 6,53</t>
+          <t>-9,7; 6,6</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-3,74%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>4,26%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>11,61%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-0,58%</t>
+          <t>-0,63%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 17,16</t>
+          <t>-10,76; 13,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,15; 24,87</t>
+          <t>3,8; 30,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 15,65</t>
+          <t>-25,05; 10,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 14,57</t>
+          <t>-6,1; 16,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,14; 30,45</t>
+          <t>1,77; 24,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 12,32</t>
+          <t>-7,58; 17,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 11,35</t>
+          <t>-5,39; 12,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,31; 21,87</t>
+          <t>4,9; 22,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 9,13</t>
+          <t>-12,63; 9,1</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4,39</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10,68</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-5,58</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>13,08</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>10,68</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 6,78</t>
+          <t>-6,62; 15,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,88; 23,56</t>
+          <t>-0,73; 21,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 8,47</t>
+          <t>-12,14; 12,74</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 15,78</t>
+          <t>-18,19; 7,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 22,11</t>
+          <t>2,99; 22,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 13,55</t>
+          <t>-15,79; 7,79</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 8,57</t>
+          <t>-8,2; 8,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,78; 19,13</t>
+          <t>4,37; 19,18</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 7,42</t>
+          <t>-10,53; 6,76</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-7,28%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>17,06%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-4,33%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>-5,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,78%</t>
+          <t>-2,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 9,5</t>
+          <t>-8,58; 23,02</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,57; 34,04</t>
+          <t>-0,8; 32,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 11,64</t>
+          <t>-15,57; 19,16</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 22,94</t>
+          <t>-23,29; 9,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 33,36</t>
+          <t>3,62; 32,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 19,72</t>
+          <t>-19,35; 11,3</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 11,9</t>
+          <t>-10,29; 12,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,83; 27,07</t>
+          <t>5,52; 26,83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 10,22</t>
+          <t>-13,32; 9,54</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,34</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8,97</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,99</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-2,69</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>8,55</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>8,97</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-1,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,89</t>
+          <t>-5,01; 2,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,44; 12,2</t>
+          <t>5,56; 12,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 3,88</t>
+          <t>-5,47; 3,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 2,44</t>
+          <t>-6,06; 1,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,68</t>
+          <t>4,94; 11,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,4</t>
+          <t>-5,04; 2,54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,69</t>
+          <t>-4,75; 0,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,15</t>
+          <t>6,45; 11,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,34</t>
+          <t>-4,16; 1,48</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-1,74%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-1,28%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-3,45%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>10,95%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-0,65%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-1,74%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0,87%</t>
+          <t>-1,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-0,79%</t>
+          <t>-1,5%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 1,17</t>
+          <t>-6,44; 2,9</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6,74; 16,03</t>
+          <t>7,14; 16,59</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,02</t>
+          <t>-6,98; 4,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 3,29</t>
+          <t>-7,61; 1,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,48; 17,06</t>
+          <t>6,21; 15,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 4,53</t>
+          <t>-6,4; 3,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,83</t>
+          <t>-6,03; 0,55</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,16; 14,73</t>
+          <t>8,17; 14,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,08</t>
+          <t>-5,33; 1,92</t>
         </is>
       </c>
     </row>
